--- a/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
+++ b/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahr\eclipse-workspace\wipro-assignment\capstone_guru99\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031F47E9-5862-44F1-92E6-D8A20F20BA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E7B686-FC01-4E69-A2A4-27B319E96552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerID" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,106 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>customerId</t>
   </si>
-  <si>
-    <t>33840</t>
-  </si>
-  <si>
-    <t>11813</t>
-  </si>
-  <si>
-    <t>12273</t>
-  </si>
-  <si>
-    <t>54874</t>
-  </si>
-  <si>
-    <t>85151</t>
-  </si>
-  <si>
-    <t>26320</t>
-  </si>
-  <si>
-    <t>7250</t>
-  </si>
-  <si>
-    <t>93087</t>
-  </si>
-  <si>
-    <t>80408</t>
-  </si>
-  <si>
-    <t>33910</t>
-  </si>
-  <si>
-    <t>37316</t>
-  </si>
-  <si>
-    <t>91710</t>
-  </si>
-  <si>
-    <t>77332</t>
-  </si>
-  <si>
-    <t>2453</t>
-  </si>
-  <si>
-    <t>20108</t>
-  </si>
-  <si>
-    <t>96570</t>
-  </si>
-  <si>
-    <t>41497</t>
-  </si>
-  <si>
-    <t>21852</t>
-  </si>
-  <si>
-    <t>73569</t>
-  </si>
-  <si>
-    <t>73361</t>
-  </si>
-  <si>
-    <t>67130</t>
-  </si>
-  <si>
-    <t>98117</t>
-  </si>
-  <si>
-    <t>5886</t>
-  </si>
-  <si>
-    <t>80267</t>
-  </si>
-  <si>
-    <t>69324</t>
-  </si>
-  <si>
-    <t>59146</t>
-  </si>
-  <si>
-    <t>84156</t>
-  </si>
-  <si>
-    <t>27591</t>
-  </si>
-  <si>
-    <t>92870</t>
-  </si>
-  <si>
-    <t>72290</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -439,22 +348,22 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="11.0"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>29</v>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>9660</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>30</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>5792</v>
       </c>
     </row>
   </sheetData>

--- a/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
+++ b/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E7B686-FC01-4E69-A2A4-27B319E96552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DCD218-30FF-4C8F-A1D2-3AEF96643170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4890" yWindow="2280" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerID" sheetId="1" r:id="rId1"/>

--- a/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
+++ b/guru99_automation/target/test-classes/testdata/CustomerId.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,15 +25,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>customerId</t>
   </si>
+  <si>
+    <t>4453</t>
+  </si>
+  <si>
+    <t>93030</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -348,22 +355,22 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9660</v>
+      <c r="A2" t="s" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5792</v>
+      <c r="A3" s="0" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
